--- a/public/M15A_假期申請表.xlsx
+++ b/public/M15A_假期申請表.xlsx
@@ -3,13 +3,12 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4FC21FA8-5470-44DF-88A1-491F3F79CD8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8D1C6C-31ED-4FF7-9615-9F1A77C6B276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="1" sheetId="53" r:id="rId1"/>
-    <sheet name="M15假期申請表_7,8月" sheetId="57" r:id="rId2"/>
+    <sheet name="M15假期申請表" sheetId="57" r:id="rId1"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -27,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="48">
   <si>
     <t>Millennium Secondary School</t>
   </si>
@@ -88,95 +87,25 @@
     <t>姓名 Name</t>
   </si>
   <si>
-    <t>鄧浩泉</t>
-  </si>
-  <si>
     <t>部門 Department</t>
   </si>
   <si>
-    <t>普中教學事務總統部</t>
-  </si>
-  <si>
     <t>聯絡電話 Contact Number</t>
   </si>
   <si>
     <t>職位 Position</t>
   </si>
   <si>
-    <t>教師</t>
-  </si>
-  <si>
     <t>假期申請 Leave Application</t>
   </si>
   <si>
     <t xml:space="preserve">休假期間由 Leave taken from </t>
   </si>
   <si>
-    <t>6月</t>
-  </si>
-  <si>
-    <t>10日               至 to</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">         6  </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="88"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve">月    10        日 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="72"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve">             (包括當天 )</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">           6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="88"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve">月      10   日 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="72"/>
-        <rFont val="新細明體"/>
-        <family val="1"/>
-        <charset val="136"/>
-      </rPr>
-      <t xml:space="preserve">             (包括當天 )</t>
-    </r>
-  </si>
-  <si>
     <t>共休假天數 Days taken：</t>
   </si>
   <si>
     <t>天 Days</t>
-  </si>
-  <si>
-    <t>共        3    小時hrs</t>
-  </si>
-  <si>
-    <t xml:space="preserve">                      分鐘mins</t>
-  </si>
-  <si>
-    <t>共    3        小時hrs</t>
   </si>
   <si>
     <t>休假原因 Reason for leave：</t>
@@ -1364,7 +1293,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="133">
+  <cellXfs count="130">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1414,9 +1343,6 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1573,6 +1499,159 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="14" fontId="5" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1600,166 +1679,7 @@
     <xf numFmtId="0" fontId="6" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="21" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="7" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="31" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="32" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="33" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="50" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="51" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="52" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="53" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="59" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="57" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="53" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="5" fillId="0" borderId="54" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="55" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="56" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="54" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="64" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="65" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="66" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="67" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="68" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="69" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1780,187 +1700,6 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1047750</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>527050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1479550</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>1885950</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="Picture 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1047750</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>527050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>1479550</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>1885950</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="Picture 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000003000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>1047750</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>527050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>1479550</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>1885950</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="Picture 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>1047750</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>527050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>1479550</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>1885950</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="5" name="Picture 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0000-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2427,894 +2166,6 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:S51"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="39" customHeight="1"/>
-  <cols>
-    <col min="1" max="1" width="23.6328125" style="1" customWidth="1"/>
-    <col min="2" max="2" width="40.7265625" style="1" customWidth="1"/>
-    <col min="3" max="3" width="83.90625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="15.90625" style="1" customWidth="1"/>
-    <col min="5" max="5" width="134.26953125" style="1" customWidth="1"/>
-    <col min="6" max="6" width="70.26953125" style="1" customWidth="1"/>
-    <col min="7" max="7" width="127.26953125" style="1" customWidth="1"/>
-    <col min="8" max="8" width="146.6328125" style="1" customWidth="1"/>
-    <col min="9" max="9" width="62.7265625" style="1" customWidth="1"/>
-    <col min="10" max="10" width="22" style="1" customWidth="1"/>
-    <col min="11" max="11" width="23.6328125" style="1" customWidth="1"/>
-    <col min="12" max="12" width="40.7265625" style="1" customWidth="1"/>
-    <col min="13" max="13" width="87.6328125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="15.90625" style="1" customWidth="1"/>
-    <col min="15" max="15" width="134.26953125" style="1" customWidth="1"/>
-    <col min="16" max="16" width="67.7265625" style="1" customWidth="1"/>
-    <col min="17" max="17" width="127.26953125" style="1" customWidth="1"/>
-    <col min="18" max="18" width="146.6328125" style="1" customWidth="1"/>
-    <col min="19" max="19" width="70.26953125" style="1" customWidth="1"/>
-    <col min="20" max="20" width="9" style="1" customWidth="1"/>
-    <col min="21" max="16384" width="9" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:19" ht="200.15" customHeight="1">
-      <c r="A1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="72"/>
-      <c r="K1" s="70" t="s">
-        <v>0</v>
-      </c>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
-      <c r="R1" s="71"/>
-      <c r="S1" s="72"/>
-    </row>
-    <row r="2" spans="1:19" ht="200.15" customHeight="1">
-      <c r="A2" s="73" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="75"/>
-      <c r="K2" s="73" t="s">
-        <v>1</v>
-      </c>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="74"/>
-      <c r="S2" s="75"/>
-    </row>
-    <row r="3" spans="1:19" s="2" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A3" s="79">
-        <v>1</v>
-      </c>
-      <c r="B3" s="76" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="78"/>
-      <c r="K3" s="79">
-        <v>1</v>
-      </c>
-      <c r="L3" s="76" t="s">
-        <v>2</v>
-      </c>
-      <c r="M3" s="77"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="78"/>
-    </row>
-    <row r="4" spans="1:19" s="3" customFormat="1" ht="229.5" customHeight="1">
-      <c r="A4" s="80"/>
-      <c r="B4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="5"/>
-      <c r="E4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="I4" s="7"/>
-      <c r="K4" s="80"/>
-      <c r="L4" s="4" t="s">
-        <v>3</v>
-      </c>
-      <c r="M4" s="4"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5" t="s">
-        <v>4</v>
-      </c>
-      <c r="P4" s="4"/>
-      <c r="Q4" s="6" t="s">
-        <v>5</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="S4" s="7"/>
-    </row>
-    <row r="5" spans="1:19" s="3" customFormat="1" ht="222" customHeight="1">
-      <c r="A5" s="81"/>
-      <c r="B5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="C5" s="8"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="8">
-        <v>66655606</v>
-      </c>
-      <c r="G5" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="H5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="I5" s="11"/>
-      <c r="K5" s="81"/>
-      <c r="L5" s="8" t="s">
-        <v>7</v>
-      </c>
-      <c r="M5" s="8"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="8">
-        <v>66655606</v>
-      </c>
-      <c r="Q5" s="10" t="s">
-        <v>8</v>
-      </c>
-      <c r="R5" s="9" t="s">
-        <v>9</v>
-      </c>
-      <c r="S5" s="11"/>
-    </row>
-    <row r="6" spans="1:19" s="2" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A6" s="82">
-        <v>2</v>
-      </c>
-      <c r="B6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="14"/>
-      <c r="K6" s="82">
-        <v>2</v>
-      </c>
-      <c r="L6" s="12" t="s">
-        <v>10</v>
-      </c>
-      <c r="M6" s="13"/>
-      <c r="N6" s="13"/>
-      <c r="O6" s="13"/>
-      <c r="P6" s="13"/>
-      <c r="Q6" s="13"/>
-      <c r="R6" s="13"/>
-      <c r="S6" s="14"/>
-    </row>
-    <row r="7" spans="1:19" s="3" customFormat="1" ht="289.5" customHeight="1">
-      <c r="A7" s="83"/>
-      <c r="B7" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="G7" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="H7" s="130" t="s">
-        <v>14</v>
-      </c>
-      <c r="I7" s="131"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7" s="86"/>
-      <c r="N7" s="86"/>
-      <c r="O7" s="86"/>
-      <c r="P7" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="Q7" s="16" t="s">
-        <v>13</v>
-      </c>
-      <c r="R7" s="130" t="s">
-        <v>15</v>
-      </c>
-      <c r="S7" s="131"/>
-    </row>
-    <row r="8" spans="1:19" s="3" customFormat="1" ht="229.5" customHeight="1">
-      <c r="A8" s="83"/>
-      <c r="B8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="C8" s="4"/>
-      <c r="D8" s="5"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="17" t="s">
-        <v>18</v>
-      </c>
-      <c r="H8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="I8" s="7"/>
-      <c r="K8" s="83"/>
-      <c r="L8" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="M8" s="4"/>
-      <c r="N8" s="5"/>
-      <c r="O8" s="5"/>
-      <c r="P8" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="Q8" s="17" t="s">
-        <v>20</v>
-      </c>
-      <c r="R8" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="S8" s="7"/>
-    </row>
-    <row r="9" spans="1:19" s="18" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A9" s="83"/>
-      <c r="B9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" s="83"/>
-      <c r="L9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="19"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="21"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="R9" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="S9" s="24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" s="18" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A10" s="83"/>
-      <c r="B10" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="29">
-        <v>1500</v>
-      </c>
-      <c r="H10" s="29">
-        <v>1800</v>
-      </c>
-      <c r="I10" s="30"/>
-      <c r="K10" s="83"/>
-      <c r="L10" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="M10" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="N10" s="27"/>
-      <c r="O10" s="27"/>
-      <c r="P10" s="28"/>
-      <c r="Q10" s="29">
-        <v>1500</v>
-      </c>
-      <c r="R10" s="29">
-        <v>1800</v>
-      </c>
-      <c r="S10" s="30"/>
-    </row>
-    <row r="11" spans="1:19" s="18" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A11" s="83"/>
-      <c r="B11" s="92" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="D11" s="2"/>
-      <c r="E11" s="2"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="34"/>
-      <c r="K11" s="83"/>
-      <c r="L11" s="92" t="s">
-        <v>27</v>
-      </c>
-      <c r="M11" s="31" t="s">
-        <v>28</v>
-      </c>
-      <c r="N11" s="2"/>
-      <c r="O11" s="2"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
-      <c r="S11" s="34"/>
-    </row>
-    <row r="12" spans="1:19" s="18" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A12" s="83"/>
-      <c r="B12" s="93"/>
-      <c r="C12" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="30"/>
-      <c r="K12" s="83"/>
-      <c r="L12" s="93"/>
-      <c r="M12" s="31" t="s">
-        <v>29</v>
-      </c>
-      <c r="N12" s="2"/>
-      <c r="O12" s="2"/>
-      <c r="P12" s="32"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="30"/>
-    </row>
-    <row r="13" spans="1:19" s="18" customFormat="1" ht="199.5" customHeight="1">
-      <c r="A13" s="83"/>
-      <c r="B13" s="98"/>
-      <c r="C13" s="99" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="100"/>
-      <c r="E13" s="100"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="30"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="98"/>
-      <c r="M13" s="99" t="s">
-        <v>30</v>
-      </c>
-      <c r="N13" s="100"/>
-      <c r="O13" s="100"/>
-      <c r="P13" s="101"/>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="29"/>
-      <c r="S13" s="30"/>
-    </row>
-    <row r="14" spans="1:19" s="18" customFormat="1" ht="250" customHeight="1">
-      <c r="A14" s="83"/>
-      <c r="B14" s="92" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="89" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="91"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="30"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="92" t="s">
-        <v>31</v>
-      </c>
-      <c r="M14" s="89" t="s">
-        <v>32</v>
-      </c>
-      <c r="N14" s="90"/>
-      <c r="O14" s="90"/>
-      <c r="P14" s="91"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="30"/>
-    </row>
-    <row r="15" spans="1:19" s="18" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A15" s="83"/>
-      <c r="B15" s="93"/>
-      <c r="C15" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="D15" s="2"/>
-      <c r="E15" s="2"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="30"/>
-      <c r="K15" s="83"/>
-      <c r="L15" s="93"/>
-      <c r="M15" s="31" t="s">
-        <v>33</v>
-      </c>
-      <c r="N15" s="2"/>
-      <c r="O15" s="2"/>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="29"/>
-      <c r="S15" s="30"/>
-    </row>
-    <row r="16" spans="1:19" s="18" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A16" s="83"/>
-      <c r="B16" s="93"/>
-      <c r="C16" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="37"/>
-      <c r="K16" s="83"/>
-      <c r="L16" s="93"/>
-      <c r="M16" s="31" t="s">
-        <v>34</v>
-      </c>
-      <c r="N16" s="2"/>
-      <c r="O16" s="2"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="36"/>
-      <c r="S16" s="37"/>
-    </row>
-    <row r="17" spans="1:19" s="18" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A17" s="83"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="D17" s="2"/>
-      <c r="E17" s="2"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
-      <c r="K17" s="83"/>
-      <c r="L17" s="93"/>
-      <c r="M17" s="31" t="s">
-        <v>35</v>
-      </c>
-      <c r="N17" s="2"/>
-      <c r="O17" s="2"/>
-      <c r="P17" s="2"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="38"/>
-      <c r="S17" s="39"/>
-    </row>
-    <row r="18" spans="1:19" s="18" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A18" s="83"/>
-      <c r="B18" s="93"/>
-      <c r="C18" s="95" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="96"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="97"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="41"/>
-      <c r="K18" s="83"/>
-      <c r="L18" s="93"/>
-      <c r="M18" s="95" t="s">
-        <v>36</v>
-      </c>
-      <c r="N18" s="96"/>
-      <c r="O18" s="96"/>
-      <c r="P18" s="97"/>
-      <c r="Q18" s="40"/>
-      <c r="R18" s="40"/>
-      <c r="S18" s="41"/>
-    </row>
-    <row r="19" spans="1:19" s="18" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A19" s="83"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="2"/>
-      <c r="E19" s="2"/>
-      <c r="F19" s="2"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="39"/>
-      <c r="K19" s="83"/>
-      <c r="L19" s="93"/>
-      <c r="M19" s="42" t="s">
-        <v>37</v>
-      </c>
-      <c r="N19" s="2"/>
-      <c r="O19" s="2"/>
-      <c r="P19" s="2"/>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="43"/>
-      <c r="S19" s="39"/>
-    </row>
-    <row r="20" spans="1:19" s="18" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A20" s="83"/>
-      <c r="B20" s="93"/>
-      <c r="C20" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="D20" s="2"/>
-      <c r="E20" s="2"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="45"/>
-      <c r="K20" s="83"/>
-      <c r="L20" s="93"/>
-      <c r="M20" s="31" t="s">
-        <v>38</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
-      <c r="P20" s="32"/>
-      <c r="Q20" s="44"/>
-      <c r="R20" s="44"/>
-      <c r="S20" s="45"/>
-    </row>
-    <row r="21" spans="1:19" s="18" customFormat="1" ht="188.15" customHeight="1">
-      <c r="A21" s="84"/>
-      <c r="B21" s="94"/>
-      <c r="C21" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="D21" s="2"/>
-      <c r="E21" s="2"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="46"/>
-      <c r="K21" s="84"/>
-      <c r="L21" s="94"/>
-      <c r="M21" s="31" t="s">
-        <v>39</v>
-      </c>
-      <c r="N21" s="2"/>
-      <c r="O21" s="2"/>
-      <c r="P21" s="32"/>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="46"/>
-    </row>
-    <row r="22" spans="1:19" s="2" customFormat="1" ht="132" customHeight="1">
-      <c r="A22" s="79">
-        <v>3</v>
-      </c>
-      <c r="B22" s="102" t="s">
-        <v>40</v>
-      </c>
-      <c r="C22" s="103"/>
-      <c r="D22" s="103"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="103"/>
-      <c r="G22" s="103"/>
-      <c r="H22" s="103"/>
-      <c r="I22" s="104"/>
-      <c r="K22" s="79">
-        <v>3</v>
-      </c>
-      <c r="L22" s="102" t="s">
-        <v>40</v>
-      </c>
-      <c r="M22" s="103"/>
-      <c r="N22" s="103"/>
-      <c r="O22" s="103"/>
-      <c r="P22" s="103"/>
-      <c r="Q22" s="103"/>
-      <c r="R22" s="103"/>
-      <c r="S22" s="104"/>
-    </row>
-    <row r="23" spans="1:19" s="18" customFormat="1" ht="274.5" customHeight="1">
-      <c r="A23" s="80"/>
-      <c r="B23" s="105" t="s">
-        <v>41</v>
-      </c>
-      <c r="C23" s="106"/>
-      <c r="D23" s="107" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" s="108"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="107" t="s">
-        <v>43</v>
-      </c>
-      <c r="H23" s="109"/>
-      <c r="I23" s="47"/>
-      <c r="K23" s="80"/>
-      <c r="L23" s="105" t="s">
-        <v>41</v>
-      </c>
-      <c r="M23" s="106"/>
-      <c r="N23" s="107" t="s">
-        <v>42</v>
-      </c>
-      <c r="O23" s="108"/>
-      <c r="P23" s="106"/>
-      <c r="Q23" s="107" t="s">
-        <v>43</v>
-      </c>
-      <c r="R23" s="109"/>
-      <c r="S23" s="47"/>
-    </row>
-    <row r="24" spans="1:19" s="18" customFormat="1" ht="267" customHeight="1">
-      <c r="A24" s="80"/>
-      <c r="B24" s="48"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="110" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" s="111"/>
-      <c r="F24" s="112"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="I24" s="47"/>
-      <c r="K24" s="80"/>
-      <c r="L24" s="48"/>
-      <c r="M24" s="52"/>
-      <c r="N24" s="110"/>
-      <c r="O24" s="111"/>
-      <c r="P24" s="112"/>
-      <c r="Q24" s="50"/>
-      <c r="R24" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="S24" s="47"/>
-    </row>
-    <row r="25" spans="1:19" s="18" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A25" s="80"/>
-      <c r="B25" s="53"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="113" t="s">
-        <v>46</v>
-      </c>
-      <c r="I25" s="114"/>
-      <c r="K25" s="80"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="56"/>
-      <c r="P25" s="54"/>
-      <c r="Q25" s="57"/>
-      <c r="R25" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="S25" s="114"/>
-    </row>
-    <row r="26" spans="1:19" s="18" customFormat="1" ht="237" customHeight="1">
-      <c r="A26" s="80"/>
-      <c r="B26" s="115" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="116"/>
-      <c r="D26" s="117" t="s">
-        <v>49</v>
-      </c>
-      <c r="E26" s="118"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="H26" s="120" t="s">
-        <v>51</v>
-      </c>
-      <c r="I26" s="121"/>
-      <c r="J26" s="60"/>
-      <c r="K26" s="80"/>
-      <c r="L26" s="115" t="s">
-        <v>52</v>
-      </c>
-      <c r="M26" s="116"/>
-      <c r="N26" s="117" t="s">
-        <v>49</v>
-      </c>
-      <c r="O26" s="118"/>
-      <c r="P26" s="119"/>
-      <c r="Q26" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="R26" s="122" t="s">
-        <v>51</v>
-      </c>
-      <c r="S26" s="123"/>
-    </row>
-    <row r="27" spans="1:19" s="2" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A27" s="61" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="63"/>
-      <c r="K27" s="61" t="s">
-        <v>53</v>
-      </c>
-      <c r="L27" s="62"/>
-      <c r="M27" s="62"/>
-      <c r="N27" s="62"/>
-      <c r="O27" s="62"/>
-      <c r="P27" s="62"/>
-      <c r="Q27" s="62"/>
-      <c r="R27" s="124" t="s">
-        <v>54</v>
-      </c>
-      <c r="S27" s="125"/>
-    </row>
-    <row r="28" spans="1:19" s="18" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A28" s="58"/>
-      <c r="C28" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="J28" s="60"/>
-      <c r="K28" s="58"/>
-      <c r="M28" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="R28" s="126"/>
-      <c r="S28" s="127"/>
-    </row>
-    <row r="29" spans="1:19" ht="79.5" customHeight="1">
-      <c r="A29" s="64"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="65"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="67"/>
-      <c r="K29" s="64"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="65"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="65"/>
-      <c r="P29" s="65"/>
-      <c r="Q29" s="65"/>
-      <c r="R29" s="128"/>
-      <c r="S29" s="129"/>
-    </row>
-    <row r="50" spans="13:13">
-      <c r="M50" s="68"/>
-    </row>
-    <row r="51" spans="13:13">
-      <c r="M51" s="69"/>
-    </row>
-  </sheetData>
-  <mergeCells count="45">
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="R27:S29"/>
-    <mergeCell ref="B22:I22"/>
-    <mergeCell ref="L22:S22"/>
-    <mergeCell ref="A22:A26"/>
-    <mergeCell ref="B23:C23"/>
-    <mergeCell ref="D23:F23"/>
-    <mergeCell ref="G23:H23"/>
-    <mergeCell ref="K22:K26"/>
-    <mergeCell ref="L23:M23"/>
-    <mergeCell ref="N23:P23"/>
-    <mergeCell ref="Q23:R23"/>
-    <mergeCell ref="D24:F24"/>
-    <mergeCell ref="N24:P24"/>
-    <mergeCell ref="H25:I25"/>
-    <mergeCell ref="R25:S25"/>
-    <mergeCell ref="B26:C26"/>
-    <mergeCell ref="D26:F26"/>
-    <mergeCell ref="R7:S7"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="L11:L13"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="M13:P13"/>
-    <mergeCell ref="A6:A21"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="H7:I7"/>
-    <mergeCell ref="K6:K21"/>
-    <mergeCell ref="L7:O7"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="M14:P14"/>
-    <mergeCell ref="B14:B21"/>
-    <mergeCell ref="L14:L21"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="M18:P18"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="K2:S2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="L3:S3"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="K3:K5"/>
-  </mergeCells>
-  <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
-  <pageSetup paperSize="9" scale="10" orientation="landscape" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
@@ -3346,83 +2197,83 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="184.5" customHeight="1">
-      <c r="A1" s="70" t="s">
+      <c r="A1" s="120" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71"/>
-      <c r="C1" s="71"/>
-      <c r="D1" s="71"/>
-      <c r="E1" s="71"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="71"/>
-      <c r="H1" s="71"/>
-      <c r="I1" s="72"/>
-      <c r="K1" s="70" t="s">
+      <c r="B1" s="121"/>
+      <c r="C1" s="121"/>
+      <c r="D1" s="121"/>
+      <c r="E1" s="121"/>
+      <c r="F1" s="121"/>
+      <c r="G1" s="121"/>
+      <c r="H1" s="121"/>
+      <c r="I1" s="122"/>
+      <c r="K1" s="120" t="s">
         <v>0</v>
       </c>
-      <c r="L1" s="71"/>
-      <c r="M1" s="71"/>
-      <c r="N1" s="71"/>
-      <c r="O1" s="71"/>
-      <c r="P1" s="71"/>
-      <c r="Q1" s="71"/>
-      <c r="R1" s="71"/>
-      <c r="S1" s="72"/>
+      <c r="L1" s="121"/>
+      <c r="M1" s="121"/>
+      <c r="N1" s="121"/>
+      <c r="O1" s="121"/>
+      <c r="P1" s="121"/>
+      <c r="Q1" s="121"/>
+      <c r="R1" s="121"/>
+      <c r="S1" s="122"/>
     </row>
     <row r="2" spans="1:19" ht="139.5" customHeight="1">
-      <c r="A2" s="73" t="s">
+      <c r="A2" s="123" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="74"/>
-      <c r="C2" s="74"/>
-      <c r="D2" s="74"/>
-      <c r="E2" s="74"/>
-      <c r="F2" s="74"/>
-      <c r="G2" s="74"/>
-      <c r="H2" s="74"/>
-      <c r="I2" s="75"/>
-      <c r="K2" s="73" t="s">
+      <c r="B2" s="124"/>
+      <c r="C2" s="124"/>
+      <c r="D2" s="124"/>
+      <c r="E2" s="124"/>
+      <c r="F2" s="124"/>
+      <c r="G2" s="124"/>
+      <c r="H2" s="124"/>
+      <c r="I2" s="125"/>
+      <c r="K2" s="123" t="s">
         <v>1</v>
       </c>
-      <c r="L2" s="74"/>
-      <c r="M2" s="74"/>
-      <c r="N2" s="74"/>
-      <c r="O2" s="74"/>
-      <c r="P2" s="74"/>
-      <c r="Q2" s="74"/>
-      <c r="R2" s="74"/>
-      <c r="S2" s="75"/>
+      <c r="L2" s="124"/>
+      <c r="M2" s="124"/>
+      <c r="N2" s="124"/>
+      <c r="O2" s="124"/>
+      <c r="P2" s="124"/>
+      <c r="Q2" s="124"/>
+      <c r="R2" s="124"/>
+      <c r="S2" s="125"/>
     </row>
     <row r="3" spans="1:19" s="2" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A3" s="79">
+      <c r="A3" s="87">
         <v>1</v>
       </c>
-      <c r="B3" s="76" t="s">
+      <c r="B3" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="C3" s="77"/>
-      <c r="D3" s="77"/>
-      <c r="E3" s="77"/>
-      <c r="F3" s="77"/>
-      <c r="G3" s="77"/>
-      <c r="H3" s="77"/>
-      <c r="I3" s="78"/>
-      <c r="K3" s="79">
+      <c r="C3" s="127"/>
+      <c r="D3" s="127"/>
+      <c r="E3" s="127"/>
+      <c r="F3" s="127"/>
+      <c r="G3" s="127"/>
+      <c r="H3" s="127"/>
+      <c r="I3" s="128"/>
+      <c r="K3" s="87">
         <v>1</v>
       </c>
-      <c r="L3" s="76" t="s">
+      <c r="L3" s="126" t="s">
         <v>2</v>
       </c>
-      <c r="M3" s="77"/>
-      <c r="N3" s="77"/>
-      <c r="O3" s="77"/>
-      <c r="P3" s="77"/>
-      <c r="Q3" s="77"/>
-      <c r="R3" s="77"/>
-      <c r="S3" s="78"/>
+      <c r="M3" s="127"/>
+      <c r="N3" s="127"/>
+      <c r="O3" s="127"/>
+      <c r="P3" s="127"/>
+      <c r="Q3" s="127"/>
+      <c r="R3" s="127"/>
+      <c r="S3" s="128"/>
     </row>
     <row r="4" spans="1:19" s="3" customFormat="1" ht="229.5" customHeight="1">
-      <c r="A4" s="80"/>
+      <c r="A4" s="88"/>
       <c r="B4" s="4" t="s">
         <v>3</v>
       </c>
@@ -3431,11 +2282,11 @@
       <c r="E4" s="5"/>
       <c r="F4" s="4"/>
       <c r="G4" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="7"/>
-      <c r="K4" s="80"/>
+      <c r="K4" s="88"/>
       <c r="L4" s="4" t="s">
         <v>3</v>
       </c>
@@ -3444,45 +2295,45 @@
       <c r="O4" s="5"/>
       <c r="P4" s="4"/>
       <c r="Q4" s="6" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="R4" s="5"/>
       <c r="S4" s="7"/>
     </row>
     <row r="5" spans="1:19" s="3" customFormat="1" ht="222" customHeight="1">
-      <c r="A5" s="81"/>
+      <c r="A5" s="129"/>
       <c r="B5" s="8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="C5" s="8"/>
       <c r="D5" s="9"/>
       <c r="E5" s="9"/>
       <c r="F5" s="8"/>
       <c r="G5" s="10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="11"/>
-      <c r="K5" s="81"/>
+      <c r="K5" s="129"/>
       <c r="L5" s="8" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="M5" s="8"/>
       <c r="N5" s="9"/>
       <c r="O5" s="9"/>
       <c r="P5" s="8"/>
       <c r="Q5" s="10" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="R5" s="9"/>
       <c r="S5" s="11"/>
     </row>
     <row r="6" spans="1:19" s="2" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A6" s="82">
+      <c r="A6" s="108">
         <v>2</v>
       </c>
       <c r="B6" s="12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="C6" s="13"/>
       <c r="D6" s="13"/>
@@ -3491,11 +2342,11 @@
       <c r="G6" s="13"/>
       <c r="H6" s="13"/>
       <c r="I6" s="14"/>
-      <c r="K6" s="82">
+      <c r="K6" s="108">
         <v>2</v>
       </c>
       <c r="L6" s="12" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="M6" s="13"/>
       <c r="N6" s="13"/>
@@ -3506,623 +2357,644 @@
       <c r="S6" s="14"/>
     </row>
     <row r="7" spans="1:19" s="3" customFormat="1" ht="207" customHeight="1">
-      <c r="A7" s="83"/>
-      <c r="B7" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="C7" s="86"/>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
+      <c r="A7" s="109"/>
+      <c r="B7" s="111" t="s">
+        <v>8</v>
+      </c>
+      <c r="C7" s="112"/>
+      <c r="D7" s="112"/>
+      <c r="E7" s="112"/>
       <c r="F7" s="15"/>
-      <c r="G7" s="87" t="s">
-        <v>56</v>
-      </c>
-      <c r="H7" s="87"/>
-      <c r="I7" s="88"/>
-      <c r="K7" s="83"/>
-      <c r="L7" s="85" t="s">
-        <v>11</v>
-      </c>
-      <c r="M7" s="86"/>
-      <c r="N7" s="86"/>
-      <c r="O7" s="86"/>
+      <c r="G7" s="99" t="s">
+        <v>46</v>
+      </c>
+      <c r="H7" s="99"/>
+      <c r="I7" s="100"/>
+      <c r="K7" s="109"/>
+      <c r="L7" s="111" t="s">
+        <v>8</v>
+      </c>
+      <c r="M7" s="112"/>
+      <c r="N7" s="112"/>
+      <c r="O7" s="112"/>
       <c r="P7" s="15"/>
-      <c r="Q7" s="87" t="str">
+      <c r="Q7" s="99" t="str">
         <f>G7</f>
         <v xml:space="preserve">  至 to  </v>
       </c>
-      <c r="R7" s="87"/>
-      <c r="S7" s="88"/>
+      <c r="R7" s="99"/>
+      <c r="S7" s="100"/>
     </row>
     <row r="8" spans="1:19" s="3" customFormat="1" ht="229.5" customHeight="1">
-      <c r="A8" s="83"/>
+      <c r="A8" s="109"/>
       <c r="B8" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="C8" s="4"/>
       <c r="D8" s="5"/>
       <c r="E8" s="5"/>
       <c r="F8" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="G8" s="132" t="s">
-        <v>57</v>
-      </c>
-      <c r="H8" s="87"/>
-      <c r="I8" s="88"/>
-      <c r="K8" s="83"/>
+        <v>10</v>
+      </c>
+      <c r="G8" s="107" t="s">
+        <v>47</v>
+      </c>
+      <c r="H8" s="99"/>
+      <c r="I8" s="100"/>
+      <c r="K8" s="109"/>
       <c r="L8" s="4" t="s">
-        <v>16</v>
+        <v>9</v>
       </c>
       <c r="M8" s="4"/>
       <c r="N8" s="5"/>
       <c r="O8" s="5"/>
       <c r="P8" s="16" t="s">
+        <v>10</v>
+      </c>
+      <c r="Q8" s="107" t="s">
+        <v>47</v>
+      </c>
+      <c r="R8" s="99"/>
+      <c r="S8" s="100"/>
+    </row>
+    <row r="9" spans="1:19" s="17" customFormat="1" ht="200.15" customHeight="1">
+      <c r="A9" s="109"/>
+      <c r="B9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="C9" s="18"/>
+      <c r="D9" s="19"/>
+      <c r="E9" s="20"/>
+      <c r="F9" s="18"/>
+      <c r="G9" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="H9" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="I9" s="23" t="s">
+        <v>14</v>
+      </c>
+      <c r="K9" s="109"/>
+      <c r="L9" s="4" t="s">
+        <v>11</v>
+      </c>
+      <c r="M9" s="18"/>
+      <c r="N9" s="19"/>
+      <c r="O9" s="20"/>
+      <c r="P9" s="18"/>
+      <c r="Q9" s="21" t="s">
+        <v>12</v>
+      </c>
+      <c r="R9" s="22" t="s">
+        <v>13</v>
+      </c>
+      <c r="S9" s="23" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19" s="17" customFormat="1" ht="200.15" customHeight="1">
+      <c r="A10" s="109"/>
+      <c r="B10" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="C10" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="26"/>
+      <c r="E10" s="26"/>
+      <c r="F10" s="27"/>
+      <c r="G10" s="28"/>
+      <c r="H10" s="28"/>
+      <c r="I10" s="29"/>
+      <c r="K10" s="109"/>
+      <c r="L10" s="24" t="s">
+        <v>15</v>
+      </c>
+      <c r="M10" s="25" t="s">
+        <v>16</v>
+      </c>
+      <c r="N10" s="26"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="27"/>
+      <c r="Q10" s="28"/>
+      <c r="R10" s="28"/>
+      <c r="S10" s="29"/>
+    </row>
+    <row r="11" spans="1:19" s="17" customFormat="1" ht="200.15" customHeight="1">
+      <c r="A11" s="109"/>
+      <c r="B11" s="101" t="s">
         <v>17</v>
       </c>
-      <c r="Q8" s="132" t="s">
-        <v>57</v>
-      </c>
-      <c r="R8" s="87"/>
-      <c r="S8" s="88"/>
-    </row>
-    <row r="9" spans="1:19" s="18" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A9" s="83"/>
-      <c r="B9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C9" s="19"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="21"/>
-      <c r="F9" s="19"/>
-      <c r="G9" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="H9" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="I9" s="24" t="s">
-        <v>24</v>
-      </c>
-      <c r="K9" s="83"/>
-      <c r="L9" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="M9" s="19"/>
-      <c r="N9" s="20"/>
-      <c r="O9" s="21"/>
-      <c r="P9" s="19"/>
-      <c r="Q9" s="22" t="s">
-        <v>22</v>
-      </c>
-      <c r="R9" s="23" t="s">
-        <v>23</v>
-      </c>
-      <c r="S9" s="24" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19" s="18" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A10" s="83"/>
-      <c r="B10" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="C10" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="D10" s="27"/>
-      <c r="E10" s="27"/>
-      <c r="F10" s="28"/>
-      <c r="G10" s="29"/>
-      <c r="H10" s="29"/>
-      <c r="I10" s="30"/>
-      <c r="K10" s="83"/>
-      <c r="L10" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="M10" s="26" t="s">
-        <v>26</v>
-      </c>
-      <c r="N10" s="27"/>
-      <c r="O10" s="27"/>
-      <c r="P10" s="28"/>
-      <c r="Q10" s="29"/>
-      <c r="R10" s="29"/>
-      <c r="S10" s="30"/>
-    </row>
-    <row r="11" spans="1:19" s="18" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A11" s="83"/>
-      <c r="B11" s="92" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" s="31" t="s">
-        <v>28</v>
+      <c r="C11" s="30" t="s">
+        <v>18</v>
       </c>
       <c r="D11" s="2"/>
       <c r="E11" s="2"/>
-      <c r="F11" s="32"/>
-      <c r="G11" s="33"/>
-      <c r="H11" s="33"/>
-      <c r="I11" s="34"/>
-      <c r="K11" s="83"/>
-      <c r="L11" s="92" t="s">
-        <v>27</v>
-      </c>
-      <c r="M11" s="31" t="s">
-        <v>28</v>
+      <c r="F11" s="31"/>
+      <c r="G11" s="32"/>
+      <c r="H11" s="32"/>
+      <c r="I11" s="33"/>
+      <c r="K11" s="109"/>
+      <c r="L11" s="101" t="s">
+        <v>17</v>
+      </c>
+      <c r="M11" s="30" t="s">
+        <v>18</v>
       </c>
       <c r="N11" s="2"/>
       <c r="O11" s="2"/>
-      <c r="P11" s="32"/>
-      <c r="Q11" s="33"/>
-      <c r="R11" s="33"/>
-      <c r="S11" s="34"/>
+      <c r="P11" s="31"/>
+      <c r="Q11" s="32"/>
+      <c r="R11" s="32"/>
+      <c r="S11" s="33"/>
     </row>
-    <row r="12" spans="1:19" s="18" customFormat="1" ht="147" customHeight="1">
-      <c r="A12" s="83"/>
-      <c r="B12" s="93"/>
-      <c r="C12" s="31" t="s">
-        <v>29</v>
+    <row r="12" spans="1:19" s="17" customFormat="1" ht="147" customHeight="1">
+      <c r="A12" s="109"/>
+      <c r="B12" s="102"/>
+      <c r="C12" s="30" t="s">
+        <v>19</v>
       </c>
       <c r="D12" s="2"/>
       <c r="E12" s="2"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="29"/>
-      <c r="H12" s="29"/>
-      <c r="I12" s="30"/>
-      <c r="K12" s="83"/>
-      <c r="L12" s="93"/>
-      <c r="M12" s="31" t="s">
-        <v>29</v>
+      <c r="F12" s="31"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="29"/>
+      <c r="K12" s="109"/>
+      <c r="L12" s="102"/>
+      <c r="M12" s="30" t="s">
+        <v>19</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" s="2"/>
-      <c r="P12" s="32"/>
-      <c r="Q12" s="29"/>
-      <c r="R12" s="29"/>
-      <c r="S12" s="30"/>
+      <c r="P12" s="31"/>
+      <c r="Q12" s="28"/>
+      <c r="R12" s="28"/>
+      <c r="S12" s="29"/>
     </row>
-    <row r="13" spans="1:19" s="18" customFormat="1" ht="154.5" customHeight="1">
-      <c r="A13" s="83"/>
-      <c r="B13" s="98"/>
-      <c r="C13" s="99" t="s">
-        <v>30</v>
-      </c>
-      <c r="D13" s="100"/>
-      <c r="E13" s="100"/>
-      <c r="F13" s="101"/>
-      <c r="G13" s="29"/>
-      <c r="H13" s="29"/>
-      <c r="I13" s="30"/>
-      <c r="K13" s="83"/>
-      <c r="L13" s="98"/>
-      <c r="M13" s="99" t="s">
-        <v>30</v>
-      </c>
-      <c r="N13" s="100"/>
-      <c r="O13" s="100"/>
-      <c r="P13" s="101"/>
-      <c r="Q13" s="29"/>
-      <c r="R13" s="29"/>
-      <c r="S13" s="30"/>
+    <row r="13" spans="1:19" s="17" customFormat="1" ht="154.5" customHeight="1">
+      <c r="A13" s="109"/>
+      <c r="B13" s="103"/>
+      <c r="C13" s="104" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="105"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="106"/>
+      <c r="G13" s="28"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="29"/>
+      <c r="K13" s="109"/>
+      <c r="L13" s="103"/>
+      <c r="M13" s="104" t="s">
+        <v>20</v>
+      </c>
+      <c r="N13" s="105"/>
+      <c r="O13" s="105"/>
+      <c r="P13" s="106"/>
+      <c r="Q13" s="28"/>
+      <c r="R13" s="28"/>
+      <c r="S13" s="29"/>
     </row>
-    <row r="14" spans="1:19" s="18" customFormat="1" ht="219.75" customHeight="1">
-      <c r="A14" s="83"/>
-      <c r="B14" s="92" t="s">
-        <v>31</v>
-      </c>
-      <c r="C14" s="89" t="s">
-        <v>32</v>
-      </c>
-      <c r="D14" s="90"/>
-      <c r="E14" s="90"/>
-      <c r="F14" s="91"/>
-      <c r="G14" s="29"/>
-      <c r="H14" s="29"/>
-      <c r="I14" s="30"/>
-      <c r="K14" s="83"/>
-      <c r="L14" s="92" t="s">
-        <v>31</v>
-      </c>
-      <c r="M14" s="89" t="s">
-        <v>32</v>
-      </c>
-      <c r="N14" s="90"/>
-      <c r="O14" s="90"/>
-      <c r="P14" s="91"/>
-      <c r="Q14" s="29"/>
-      <c r="R14" s="29"/>
-      <c r="S14" s="30"/>
+    <row r="14" spans="1:19" s="17" customFormat="1" ht="219.75" customHeight="1">
+      <c r="A14" s="109"/>
+      <c r="B14" s="101" t="s">
+        <v>21</v>
+      </c>
+      <c r="C14" s="113" t="s">
+        <v>22</v>
+      </c>
+      <c r="D14" s="114"/>
+      <c r="E14" s="114"/>
+      <c r="F14" s="115"/>
+      <c r="G14" s="28"/>
+      <c r="H14" s="28"/>
+      <c r="I14" s="29"/>
+      <c r="K14" s="109"/>
+      <c r="L14" s="101" t="s">
+        <v>21</v>
+      </c>
+      <c r="M14" s="113" t="s">
+        <v>22</v>
+      </c>
+      <c r="N14" s="114"/>
+      <c r="O14" s="114"/>
+      <c r="P14" s="115"/>
+      <c r="Q14" s="28"/>
+      <c r="R14" s="28"/>
+      <c r="S14" s="29"/>
     </row>
-    <row r="15" spans="1:19" s="18" customFormat="1" ht="157.5" customHeight="1">
-      <c r="A15" s="83"/>
-      <c r="B15" s="93"/>
-      <c r="C15" s="31" t="s">
-        <v>33</v>
+    <row r="15" spans="1:19" s="17" customFormat="1" ht="157.5" customHeight="1">
+      <c r="A15" s="109"/>
+      <c r="B15" s="102"/>
+      <c r="C15" s="30" t="s">
+        <v>23</v>
       </c>
       <c r="D15" s="2"/>
       <c r="E15" s="2"/>
-      <c r="F15" s="32"/>
-      <c r="G15" s="29"/>
-      <c r="H15" s="29"/>
-      <c r="I15" s="30"/>
-      <c r="K15" s="83"/>
-      <c r="L15" s="93"/>
-      <c r="M15" s="31" t="s">
-        <v>33</v>
+      <c r="F15" s="31"/>
+      <c r="G15" s="28"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="29"/>
+      <c r="K15" s="109"/>
+      <c r="L15" s="102"/>
+      <c r="M15" s="30" t="s">
+        <v>23</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
-      <c r="P15" s="32"/>
-      <c r="Q15" s="29"/>
-      <c r="R15" s="29"/>
-      <c r="S15" s="30"/>
+      <c r="P15" s="31"/>
+      <c r="Q15" s="28"/>
+      <c r="R15" s="28"/>
+      <c r="S15" s="29"/>
     </row>
-    <row r="16" spans="1:19" s="18" customFormat="1" ht="120" customHeight="1">
-      <c r="A16" s="83"/>
-      <c r="B16" s="93"/>
-      <c r="C16" s="31" t="s">
-        <v>34</v>
+    <row r="16" spans="1:19" s="17" customFormat="1" ht="120" customHeight="1">
+      <c r="A16" s="109"/>
+      <c r="B16" s="102"/>
+      <c r="C16" s="30" t="s">
+        <v>24</v>
       </c>
       <c r="D16" s="2"/>
       <c r="E16" s="2"/>
-      <c r="F16" s="32"/>
-      <c r="G16" s="35"/>
-      <c r="H16" s="36"/>
-      <c r="I16" s="37"/>
-      <c r="K16" s="83"/>
-      <c r="L16" s="93"/>
-      <c r="M16" s="31" t="s">
-        <v>34</v>
+      <c r="F16" s="31"/>
+      <c r="G16" s="34"/>
+      <c r="H16" s="35"/>
+      <c r="I16" s="36"/>
+      <c r="K16" s="109"/>
+      <c r="L16" s="102"/>
+      <c r="M16" s="30" t="s">
+        <v>24</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
-      <c r="P16" s="32"/>
-      <c r="Q16" s="35"/>
-      <c r="R16" s="36"/>
-      <c r="S16" s="37"/>
+      <c r="P16" s="31"/>
+      <c r="Q16" s="34"/>
+      <c r="R16" s="35"/>
+      <c r="S16" s="36"/>
     </row>
-    <row r="17" spans="1:19" s="18" customFormat="1" ht="112.5" customHeight="1">
-      <c r="A17" s="83"/>
-      <c r="B17" s="93"/>
-      <c r="C17" s="31" t="s">
-        <v>35</v>
+    <row r="17" spans="1:19" s="17" customFormat="1" ht="112.5" customHeight="1">
+      <c r="A17" s="109"/>
+      <c r="B17" s="102"/>
+      <c r="C17" s="30" t="s">
+        <v>25</v>
       </c>
       <c r="D17" s="2"/>
       <c r="E17" s="2"/>
       <c r="F17" s="2"/>
-      <c r="G17" s="35"/>
-      <c r="H17" s="38"/>
-      <c r="I17" s="39"/>
-      <c r="K17" s="83"/>
-      <c r="L17" s="93"/>
-      <c r="M17" s="31" t="s">
-        <v>35</v>
+      <c r="G17" s="34"/>
+      <c r="H17" s="37"/>
+      <c r="I17" s="38"/>
+      <c r="K17" s="109"/>
+      <c r="L17" s="102"/>
+      <c r="M17" s="30" t="s">
+        <v>25</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" s="2"/>
-      <c r="Q17" s="35"/>
-      <c r="R17" s="38"/>
-      <c r="S17" s="39"/>
+      <c r="Q17" s="34"/>
+      <c r="R17" s="37"/>
+      <c r="S17" s="38"/>
     </row>
-    <row r="18" spans="1:19" s="18" customFormat="1" ht="165" customHeight="1">
-      <c r="A18" s="83"/>
-      <c r="B18" s="93"/>
-      <c r="C18" s="95" t="s">
-        <v>36</v>
-      </c>
-      <c r="D18" s="96"/>
-      <c r="E18" s="96"/>
-      <c r="F18" s="97"/>
-      <c r="G18" s="40"/>
-      <c r="H18" s="40"/>
-      <c r="I18" s="41"/>
-      <c r="K18" s="83"/>
-      <c r="L18" s="93"/>
-      <c r="M18" s="95" t="s">
-        <v>36</v>
-      </c>
-      <c r="N18" s="96"/>
-      <c r="O18" s="96"/>
-      <c r="P18" s="97"/>
-      <c r="Q18" s="40"/>
-      <c r="R18" s="40"/>
-      <c r="S18" s="41"/>
+    <row r="18" spans="1:19" s="17" customFormat="1" ht="165" customHeight="1">
+      <c r="A18" s="109"/>
+      <c r="B18" s="102"/>
+      <c r="C18" s="117" t="s">
+        <v>26</v>
+      </c>
+      <c r="D18" s="118"/>
+      <c r="E18" s="118"/>
+      <c r="F18" s="119"/>
+      <c r="G18" s="39"/>
+      <c r="H18" s="39"/>
+      <c r="I18" s="40"/>
+      <c r="K18" s="109"/>
+      <c r="L18" s="102"/>
+      <c r="M18" s="117" t="s">
+        <v>26</v>
+      </c>
+      <c r="N18" s="118"/>
+      <c r="O18" s="118"/>
+      <c r="P18" s="119"/>
+      <c r="Q18" s="39"/>
+      <c r="R18" s="39"/>
+      <c r="S18" s="40"/>
     </row>
-    <row r="19" spans="1:19" s="18" customFormat="1" ht="157.5" customHeight="1">
-      <c r="A19" s="83"/>
-      <c r="B19" s="93"/>
-      <c r="C19" s="42" t="s">
-        <v>37</v>
+    <row r="19" spans="1:19" s="17" customFormat="1" ht="157.5" customHeight="1">
+      <c r="A19" s="109"/>
+      <c r="B19" s="102"/>
+      <c r="C19" s="41" t="s">
+        <v>27</v>
       </c>
       <c r="D19" s="2"/>
       <c r="E19" s="2"/>
       <c r="F19" s="2"/>
-      <c r="G19" s="43"/>
-      <c r="H19" s="43"/>
-      <c r="I19" s="39"/>
-      <c r="K19" s="83"/>
-      <c r="L19" s="93"/>
-      <c r="M19" s="42" t="s">
-        <v>37</v>
+      <c r="G19" s="42"/>
+      <c r="H19" s="42"/>
+      <c r="I19" s="38"/>
+      <c r="K19" s="109"/>
+      <c r="L19" s="102"/>
+      <c r="M19" s="41" t="s">
+        <v>27</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" s="2"/>
       <c r="P19" s="2"/>
-      <c r="Q19" s="43"/>
-      <c r="R19" s="43"/>
-      <c r="S19" s="39"/>
+      <c r="Q19" s="42"/>
+      <c r="R19" s="42"/>
+      <c r="S19" s="38"/>
     </row>
-    <row r="20" spans="1:19" s="18" customFormat="1" ht="150" customHeight="1">
-      <c r="A20" s="83"/>
-      <c r="B20" s="93"/>
-      <c r="C20" s="31" t="s">
-        <v>38</v>
+    <row r="20" spans="1:19" s="17" customFormat="1" ht="150" customHeight="1">
+      <c r="A20" s="109"/>
+      <c r="B20" s="102"/>
+      <c r="C20" s="30" t="s">
+        <v>28</v>
       </c>
       <c r="D20" s="2"/>
       <c r="E20" s="2"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="44"/>
-      <c r="H20" s="44"/>
-      <c r="I20" s="45"/>
-      <c r="K20" s="83"/>
-      <c r="L20" s="93"/>
-      <c r="M20" s="31" t="s">
-        <v>38</v>
+      <c r="F20" s="31"/>
+      <c r="G20" s="43"/>
+      <c r="H20" s="43"/>
+      <c r="I20" s="44"/>
+      <c r="K20" s="109"/>
+      <c r="L20" s="102"/>
+      <c r="M20" s="30" t="s">
+        <v>28</v>
       </c>
       <c r="N20" s="2"/>
       <c r="O20" s="2"/>
-      <c r="P20" s="32"/>
-      <c r="Q20" s="44"/>
-      <c r="R20" s="44"/>
-      <c r="S20" s="45"/>
+      <c r="P20" s="31"/>
+      <c r="Q20" s="43"/>
+      <c r="R20" s="43"/>
+      <c r="S20" s="44"/>
     </row>
-    <row r="21" spans="1:19" s="18" customFormat="1" ht="127.5" customHeight="1">
-      <c r="A21" s="84"/>
-      <c r="B21" s="94"/>
-      <c r="C21" s="31" t="s">
-        <v>39</v>
+    <row r="21" spans="1:19" s="17" customFormat="1" ht="127.5" customHeight="1">
+      <c r="A21" s="110"/>
+      <c r="B21" s="116"/>
+      <c r="C21" s="30" t="s">
+        <v>29</v>
       </c>
       <c r="D21" s="2"/>
       <c r="E21" s="2"/>
-      <c r="F21" s="32"/>
-      <c r="G21" s="35"/>
-      <c r="H21" s="35"/>
-      <c r="I21" s="46"/>
-      <c r="K21" s="84"/>
-      <c r="L21" s="94"/>
-      <c r="M21" s="31" t="s">
-        <v>39</v>
+      <c r="F21" s="31"/>
+      <c r="G21" s="34"/>
+      <c r="H21" s="34"/>
+      <c r="I21" s="45"/>
+      <c r="K21" s="110"/>
+      <c r="L21" s="116"/>
+      <c r="M21" s="30" t="s">
+        <v>29</v>
       </c>
       <c r="N21" s="2"/>
       <c r="O21" s="2"/>
-      <c r="P21" s="32"/>
-      <c r="Q21" s="35"/>
-      <c r="R21" s="35"/>
-      <c r="S21" s="46"/>
+      <c r="P21" s="31"/>
+      <c r="Q21" s="34"/>
+      <c r="R21" s="34"/>
+      <c r="S21" s="45"/>
     </row>
     <row r="22" spans="1:19" s="2" customFormat="1" ht="132" customHeight="1">
-      <c r="A22" s="79">
+      <c r="A22" s="87">
         <v>3</v>
       </c>
-      <c r="B22" s="102" t="s">
+      <c r="B22" s="84" t="s">
+        <v>30</v>
+      </c>
+      <c r="C22" s="85"/>
+      <c r="D22" s="85"/>
+      <c r="E22" s="85"/>
+      <c r="F22" s="85"/>
+      <c r="G22" s="85"/>
+      <c r="H22" s="85"/>
+      <c r="I22" s="86"/>
+      <c r="K22" s="87">
+        <v>3</v>
+      </c>
+      <c r="L22" s="84" t="s">
+        <v>30</v>
+      </c>
+      <c r="M22" s="85"/>
+      <c r="N22" s="85"/>
+      <c r="O22" s="85"/>
+      <c r="P22" s="85"/>
+      <c r="Q22" s="85"/>
+      <c r="R22" s="85"/>
+      <c r="S22" s="86"/>
+    </row>
+    <row r="23" spans="1:19" s="17" customFormat="1" ht="229.5" customHeight="1">
+      <c r="A23" s="88"/>
+      <c r="B23" s="89" t="s">
+        <v>31</v>
+      </c>
+      <c r="C23" s="90"/>
+      <c r="D23" s="91" t="s">
+        <v>32</v>
+      </c>
+      <c r="E23" s="92"/>
+      <c r="F23" s="90"/>
+      <c r="G23" s="91" t="s">
+        <v>33</v>
+      </c>
+      <c r="H23" s="93"/>
+      <c r="I23" s="46"/>
+      <c r="K23" s="88"/>
+      <c r="L23" s="89" t="s">
+        <v>31</v>
+      </c>
+      <c r="M23" s="90"/>
+      <c r="N23" s="91" t="s">
+        <v>32</v>
+      </c>
+      <c r="O23" s="92"/>
+      <c r="P23" s="90"/>
+      <c r="Q23" s="91" t="s">
+        <v>33</v>
+      </c>
+      <c r="R23" s="93"/>
+      <c r="S23" s="46"/>
+    </row>
+    <row r="24" spans="1:19" s="17" customFormat="1" ht="199.5" customHeight="1">
+      <c r="A24" s="88"/>
+      <c r="B24" s="47"/>
+      <c r="C24" s="48"/>
+      <c r="D24" s="94" t="s">
+        <v>34</v>
+      </c>
+      <c r="E24" s="95"/>
+      <c r="F24" s="96"/>
+      <c r="G24" s="49"/>
+      <c r="H24" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="I24" s="46"/>
+      <c r="K24" s="88"/>
+      <c r="L24" s="47"/>
+      <c r="M24" s="51"/>
+      <c r="N24" s="94"/>
+      <c r="O24" s="95"/>
+      <c r="P24" s="96"/>
+      <c r="Q24" s="49"/>
+      <c r="R24" s="50" t="s">
+        <v>35</v>
+      </c>
+      <c r="S24" s="46"/>
+    </row>
+    <row r="25" spans="1:19" s="17" customFormat="1" ht="124.5" customHeight="1">
+      <c r="A25" s="88"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="53"/>
+      <c r="D25" s="54"/>
+      <c r="E25" s="55"/>
+      <c r="F25" s="53"/>
+      <c r="G25" s="56"/>
+      <c r="H25" s="97" t="s">
+        <v>36</v>
+      </c>
+      <c r="I25" s="98"/>
+      <c r="K25" s="88"/>
+      <c r="L25" s="57"/>
+      <c r="M25" s="58"/>
+      <c r="N25" s="54"/>
+      <c r="O25" s="55"/>
+      <c r="P25" s="53"/>
+      <c r="Q25" s="56"/>
+      <c r="R25" s="97" t="s">
+        <v>37</v>
+      </c>
+      <c r="S25" s="98"/>
+    </row>
+    <row r="26" spans="1:19" s="17" customFormat="1" ht="274.5" customHeight="1">
+      <c r="A26" s="88"/>
+      <c r="B26" s="71" t="s">
+        <v>38</v>
+      </c>
+      <c r="C26" s="72"/>
+      <c r="D26" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="E26" s="74"/>
+      <c r="F26" s="75"/>
+      <c r="G26" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="C22" s="103"/>
-      <c r="D22" s="103"/>
-      <c r="E22" s="103"/>
-      <c r="F22" s="103"/>
-      <c r="G22" s="103"/>
-      <c r="H22" s="103"/>
-      <c r="I22" s="104"/>
-      <c r="K22" s="79">
-        <v>3</v>
-      </c>
-      <c r="L22" s="102" t="s">
+      <c r="H26" s="69" t="s">
+        <v>41</v>
+      </c>
+      <c r="I26" s="70"/>
+      <c r="J26" s="59"/>
+      <c r="K26" s="88"/>
+      <c r="L26" s="71" t="s">
+        <v>42</v>
+      </c>
+      <c r="M26" s="72"/>
+      <c r="N26" s="73" t="s">
+        <v>39</v>
+      </c>
+      <c r="O26" s="74"/>
+      <c r="P26" s="75"/>
+      <c r="Q26" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="M22" s="103"/>
-      <c r="N22" s="103"/>
-      <c r="O22" s="103"/>
-      <c r="P22" s="103"/>
-      <c r="Q22" s="103"/>
-      <c r="R22" s="103"/>
-      <c r="S22" s="104"/>
-    </row>
-    <row r="23" spans="1:19" s="18" customFormat="1" ht="229.5" customHeight="1">
-      <c r="A23" s="80"/>
-      <c r="B23" s="105" t="s">
+      <c r="R26" s="76" t="s">
         <v>41</v>
       </c>
-      <c r="C23" s="106"/>
-      <c r="D23" s="107" t="s">
-        <v>42</v>
-      </c>
-      <c r="E23" s="108"/>
-      <c r="F23" s="106"/>
-      <c r="G23" s="107" t="s">
-        <v>43</v>
-      </c>
-      <c r="H23" s="109"/>
-      <c r="I23" s="47"/>
-      <c r="K23" s="80"/>
-      <c r="L23" s="105" t="s">
-        <v>41</v>
-      </c>
-      <c r="M23" s="106"/>
-      <c r="N23" s="107" t="s">
-        <v>42</v>
-      </c>
-      <c r="O23" s="108"/>
-      <c r="P23" s="106"/>
-      <c r="Q23" s="107" t="s">
-        <v>43</v>
-      </c>
-      <c r="R23" s="109"/>
-      <c r="S23" s="47"/>
-    </row>
-    <row r="24" spans="1:19" s="18" customFormat="1" ht="199.5" customHeight="1">
-      <c r="A24" s="80"/>
-      <c r="B24" s="48"/>
-      <c r="C24" s="49"/>
-      <c r="D24" s="110" t="s">
-        <v>44</v>
-      </c>
-      <c r="E24" s="111"/>
-      <c r="F24" s="112"/>
-      <c r="G24" s="50"/>
-      <c r="H24" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="I24" s="47"/>
-      <c r="K24" s="80"/>
-      <c r="L24" s="48"/>
-      <c r="M24" s="52"/>
-      <c r="N24" s="110"/>
-      <c r="O24" s="111"/>
-      <c r="P24" s="112"/>
-      <c r="Q24" s="50"/>
-      <c r="R24" s="51" t="s">
-        <v>45</v>
-      </c>
-      <c r="S24" s="47"/>
-    </row>
-    <row r="25" spans="1:19" s="18" customFormat="1" ht="124.5" customHeight="1">
-      <c r="A25" s="80"/>
-      <c r="B25" s="53"/>
-      <c r="C25" s="54"/>
-      <c r="D25" s="55"/>
-      <c r="E25" s="56"/>
-      <c r="F25" s="54"/>
-      <c r="G25" s="57"/>
-      <c r="H25" s="113" t="s">
-        <v>46</v>
-      </c>
-      <c r="I25" s="114"/>
-      <c r="K25" s="80"/>
-      <c r="L25" s="58"/>
-      <c r="M25" s="59"/>
-      <c r="N25" s="55"/>
-      <c r="O25" s="56"/>
-      <c r="P25" s="54"/>
-      <c r="Q25" s="57"/>
-      <c r="R25" s="113" t="s">
-        <v>47</v>
-      </c>
-      <c r="S25" s="114"/>
-    </row>
-    <row r="26" spans="1:19" s="18" customFormat="1" ht="274.5" customHeight="1">
-      <c r="A26" s="80"/>
-      <c r="B26" s="115" t="s">
-        <v>48</v>
-      </c>
-      <c r="C26" s="116"/>
-      <c r="D26" s="117" t="s">
-        <v>49</v>
-      </c>
-      <c r="E26" s="118"/>
-      <c r="F26" s="119"/>
-      <c r="G26" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="H26" s="120" t="s">
-        <v>51</v>
-      </c>
-      <c r="I26" s="121"/>
-      <c r="J26" s="60"/>
-      <c r="K26" s="80"/>
-      <c r="L26" s="115" t="s">
-        <v>52</v>
-      </c>
-      <c r="M26" s="116"/>
-      <c r="N26" s="117" t="s">
-        <v>49</v>
-      </c>
-      <c r="O26" s="118"/>
-      <c r="P26" s="119"/>
-      <c r="Q26" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="R26" s="122" t="s">
-        <v>51</v>
-      </c>
-      <c r="S26" s="123"/>
+      <c r="S26" s="77"/>
     </row>
     <row r="27" spans="1:19" s="2" customFormat="1" ht="200.15" customHeight="1">
-      <c r="A27" s="61" t="s">
-        <v>53</v>
-      </c>
-      <c r="B27" s="62"/>
-      <c r="C27" s="62"/>
-      <c r="D27" s="62"/>
-      <c r="E27" s="62"/>
-      <c r="F27" s="62"/>
-      <c r="G27" s="62"/>
-      <c r="H27" s="62"/>
-      <c r="I27" s="62"/>
-      <c r="J27" s="63"/>
-      <c r="K27" s="61" t="s">
-        <v>53</v>
-      </c>
-      <c r="L27" s="62"/>
-      <c r="M27" s="62"/>
-      <c r="N27" s="62"/>
-      <c r="O27" s="62"/>
-      <c r="P27" s="62"/>
-      <c r="Q27" s="62"/>
-      <c r="R27" s="124" t="s">
-        <v>54</v>
-      </c>
-      <c r="S27" s="125"/>
+      <c r="A27" s="60" t="s">
+        <v>43</v>
+      </c>
+      <c r="B27" s="61"/>
+      <c r="C27" s="61"/>
+      <c r="D27" s="61"/>
+      <c r="E27" s="61"/>
+      <c r="F27" s="61"/>
+      <c r="G27" s="61"/>
+      <c r="H27" s="61"/>
+      <c r="I27" s="61"/>
+      <c r="J27" s="62"/>
+      <c r="K27" s="60" t="s">
+        <v>43</v>
+      </c>
+      <c r="L27" s="61"/>
+      <c r="M27" s="61"/>
+      <c r="N27" s="61"/>
+      <c r="O27" s="61"/>
+      <c r="P27" s="61"/>
+      <c r="Q27" s="61"/>
+      <c r="R27" s="78" t="s">
+        <v>44</v>
+      </c>
+      <c r="S27" s="79"/>
     </row>
-    <row r="28" spans="1:19" s="18" customFormat="1" ht="106.5" customHeight="1">
-      <c r="A28" s="58"/>
-      <c r="C28" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="J28" s="60"/>
-      <c r="K28" s="58"/>
-      <c r="M28" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="R28" s="126"/>
-      <c r="S28" s="127"/>
+    <row r="28" spans="1:19" s="17" customFormat="1" ht="106.5" customHeight="1">
+      <c r="A28" s="57"/>
+      <c r="C28" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="J28" s="59"/>
+      <c r="K28" s="57"/>
+      <c r="M28" s="17" t="s">
+        <v>45</v>
+      </c>
+      <c r="R28" s="80"/>
+      <c r="S28" s="81"/>
     </row>
     <row r="29" spans="1:19" ht="79.5" hidden="1" customHeight="1">
-      <c r="A29" s="64"/>
-      <c r="B29" s="65"/>
-      <c r="C29" s="65"/>
-      <c r="D29" s="65"/>
-      <c r="E29" s="65"/>
-      <c r="F29" s="65"/>
-      <c r="G29" s="65"/>
-      <c r="H29" s="65"/>
-      <c r="I29" s="66"/>
-      <c r="J29" s="67"/>
-      <c r="K29" s="64"/>
-      <c r="L29" s="65"/>
-      <c r="M29" s="65"/>
-      <c r="N29" s="65"/>
-      <c r="O29" s="65"/>
-      <c r="P29" s="65"/>
-      <c r="Q29" s="65"/>
-      <c r="R29" s="128"/>
-      <c r="S29" s="129"/>
+      <c r="A29" s="63"/>
+      <c r="B29" s="64"/>
+      <c r="C29" s="64"/>
+      <c r="D29" s="64"/>
+      <c r="E29" s="64"/>
+      <c r="F29" s="64"/>
+      <c r="G29" s="64"/>
+      <c r="H29" s="64"/>
+      <c r="I29" s="65"/>
+      <c r="J29" s="66"/>
+      <c r="K29" s="63"/>
+      <c r="L29" s="64"/>
+      <c r="M29" s="64"/>
+      <c r="N29" s="64"/>
+      <c r="O29" s="64"/>
+      <c r="P29" s="64"/>
+      <c r="Q29" s="64"/>
+      <c r="R29" s="82"/>
+      <c r="S29" s="83"/>
     </row>
     <row r="50" spans="13:13">
-      <c r="M50" s="68"/>
+      <c r="M50" s="67"/>
     </row>
     <row r="51" spans="13:13">
-      <c r="M51" s="69"/>
+      <c r="M51" s="68"/>
     </row>
   </sheetData>
   <mergeCells count="47">
-    <mergeCell ref="H26:I26"/>
-    <mergeCell ref="L26:M26"/>
-    <mergeCell ref="N26:P26"/>
-    <mergeCell ref="R26:S26"/>
-    <mergeCell ref="R27:S29"/>
+    <mergeCell ref="A1:I1"/>
+    <mergeCell ref="K1:S1"/>
+    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="K2:S2"/>
+    <mergeCell ref="B3:I3"/>
+    <mergeCell ref="L3:S3"/>
+    <mergeCell ref="A3:A5"/>
+    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="A6:A21"/>
+    <mergeCell ref="B7:E7"/>
+    <mergeCell ref="G7:I7"/>
+    <mergeCell ref="K6:K21"/>
+    <mergeCell ref="L7:O7"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="M14:P14"/>
+    <mergeCell ref="B14:B21"/>
+    <mergeCell ref="L14:L21"/>
+    <mergeCell ref="C18:F18"/>
+    <mergeCell ref="M18:P18"/>
+    <mergeCell ref="Q7:S7"/>
+    <mergeCell ref="B11:B13"/>
+    <mergeCell ref="L11:L13"/>
+    <mergeCell ref="C13:F13"/>
+    <mergeCell ref="M13:P13"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="Q8:S8"/>
     <mergeCell ref="B22:I22"/>
     <mergeCell ref="L22:S22"/>
     <mergeCell ref="A22:A26"/>
@@ -4139,32 +3011,11 @@
     <mergeCell ref="R25:S25"/>
     <mergeCell ref="B26:C26"/>
     <mergeCell ref="D26:F26"/>
-    <mergeCell ref="Q7:S7"/>
-    <mergeCell ref="B11:B13"/>
-    <mergeCell ref="L11:L13"/>
-    <mergeCell ref="C13:F13"/>
-    <mergeCell ref="M13:P13"/>
-    <mergeCell ref="G8:I8"/>
-    <mergeCell ref="Q8:S8"/>
-    <mergeCell ref="A6:A21"/>
-    <mergeCell ref="B7:E7"/>
-    <mergeCell ref="G7:I7"/>
-    <mergeCell ref="K6:K21"/>
-    <mergeCell ref="L7:O7"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="M14:P14"/>
-    <mergeCell ref="B14:B21"/>
-    <mergeCell ref="L14:L21"/>
-    <mergeCell ref="C18:F18"/>
-    <mergeCell ref="M18:P18"/>
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="K1:S1"/>
-    <mergeCell ref="A2:I2"/>
-    <mergeCell ref="K2:S2"/>
-    <mergeCell ref="B3:I3"/>
-    <mergeCell ref="L3:S3"/>
-    <mergeCell ref="A3:A5"/>
-    <mergeCell ref="K3:K5"/>
+    <mergeCell ref="H26:I26"/>
+    <mergeCell ref="L26:M26"/>
+    <mergeCell ref="N26:P26"/>
+    <mergeCell ref="R26:S26"/>
+    <mergeCell ref="R27:S29"/>
   </mergeCells>
   <pageMargins left="0.25" right="0.25" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" scale="10" orientation="landscape" useFirstPageNumber="1" horizontalDpi="4294967295" verticalDpi="4294967295"/>

--- a/public/M15A_假期申請表.xlsx
+++ b/public/M15A_假期申請表.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E8D1C6C-31ED-4FF7-9615-9F1A77C6B276}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CF86E06-FC8E-42D3-A20B-39E8D57CA5AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
